--- a/landmarks.xlsx
+++ b/landmarks.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="19" uniqueCount="10">
   <si>
     <t>name</t>
   </si>
@@ -40,6 +40,9 @@
   </si>
   <si>
     <t>alt</t>
+  </si>
+  <si>
+    <t>起飞点</t>
   </si>
 </sst>
 </file>
@@ -85,10 +88,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.5546875" customWidth="true"/>
+    <col min="1" max="1" width="13" customWidth="true"/>
     <col min="2" max="2" width="5" customWidth="true"/>
     <col min="3" max="3" width="5" customWidth="true"/>
     <col min="4" max="4" width="4" customWidth="true"/>
@@ -178,6 +181,20 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="0">
+        <v>0</v>
+      </c>
+      <c r="C7" s="0">
+        <v>0</v>
+      </c>
+      <c r="D7" s="0">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>